--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73703777</v>
+        <v>73703688</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731820.2064204369</v>
+        <v>731755</v>
       </c>
       <c r="R2" t="n">
-        <v>7182864.811293839</v>
+        <v>7182796</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2018-10-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>73703733</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731754.9840920451</v>
+        <v>731755</v>
       </c>
       <c r="R3" t="n">
-        <v>7182795.79448687</v>
+        <v>7182796</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2018-10-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73703688</v>
+        <v>73703787</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731754.9840920451</v>
+        <v>731889</v>
       </c>
       <c r="R4" t="n">
-        <v>7182795.79448687</v>
+        <v>7182811</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2018-10-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +969,11 @@
         <v>120435796</v>
       </c>
       <c r="B5" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1116,16 +1066,11 @@
         <v>120435797</v>
       </c>
       <c r="B6" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870463</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870448</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870453</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870471</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870500</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870482</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120435796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120435797</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2470,6 +2555,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870445</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870446</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870451</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2791,6 +2891,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870454</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870456</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3005,6 +3115,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870459</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3112,6 +3227,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870461</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870462</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3326,6 +3451,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870465</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3433,6 +3563,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870467</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3553,6 +3688,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870473</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3660,6 +3800,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870474</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3767,6 +3912,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870477</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870481</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4093,6 +4253,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870484</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4200,6 +4365,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870487</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4307,6 +4477,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870488</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870490</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870494</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4633,6 +4818,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870496</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4740,6 +4930,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870502</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4847,6 +5042,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870491</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4967,6 +5167,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870457</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5087,6 +5292,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870460</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5206,6 +5416,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870464</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5325,6 +5540,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870466</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5444,6 +5664,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870468</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5563,6 +5788,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870469</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5683,6 +5913,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870470</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5803,6 +6038,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870476</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5923,6 +6163,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870479</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6043,6 +6288,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870480</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6163,6 +6413,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870485</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6283,6 +6538,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870486</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6403,6 +6663,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870493</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6515,6 +6780,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870495</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6635,6 +6905,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870497</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6755,6 +7030,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870498</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6875,6 +7155,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870501</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6999,6 +7284,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870483</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7119,6 +7409,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870489</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7227,8 +7522,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58678</v>
+        <v>58683</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73703688</v>
+        <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lappselliden, Vb</t>
+          <t>Rengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731755</v>
+        <v>731825</v>
       </c>
       <c r="R2" t="n">
-        <v>7182796</v>
+        <v>7182853</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73703688</t>
+          <t>https://artportalen.se/Sighting/134870463</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73703733</v>
+        <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92369</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappselliden, Vb</t>
+          <t>Rengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731755</v>
+        <v>731764</v>
       </c>
       <c r="R3" t="n">
-        <v>7182796</v>
+        <v>7182800</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +891,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73703733</t>
+          <t>https://artportalen.se/Sighting/134870447</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73703787</v>
+        <v>73703688</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731889</v>
+        <v>731755</v>
       </c>
       <c r="R4" t="n">
-        <v>7182811</v>
+        <v>7182796</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,48 +1008,48 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73703787</t>
+          <t>https://artportalen.se/Sighting/73703688</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120435796</v>
+        <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappseleliden, Vb</t>
+          <t>Rengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731782</v>
+        <v>731764</v>
       </c>
       <c r="R5" t="n">
         <v>7182800</v>
@@ -1051,12 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,54 +1117,58 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120435796</t>
+          <t>https://artportalen.se/Sighting/134870448</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120435797</v>
+        <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappseleliden, Vb</t>
+          <t>Rengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731764</v>
+        <v>731774</v>
       </c>
       <c r="R6" t="n">
-        <v>7182797</v>
+        <v>7182807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1195,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,10 +1233,6514 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134870452</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134870453</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>731779</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7182821</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870453</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134870455</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>731774</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7182830</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870455</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134870471</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>731815</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7182829</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870471</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134870500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>732015</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7182697</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>73703733</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lappselliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>731755</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7182796</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703733</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>73703787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lappselliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>731889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7182811</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703787</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134870444</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>731784</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7182759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flerårig (men rätt ung, typ andra eller tredje året ser det ut som i genomskärning), mycket små porer, luktar skeletocutis</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870444</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134870449</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>731764</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7182800</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870449</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134870482</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>731937</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7182783</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870482</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120435796</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lappseleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>731782</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7182800</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120435796</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120435797</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lappseleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>731764</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7182797</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120435797</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134870445</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>731784</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7182759</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870445</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134870446</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>731758</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7182796</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870446</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134870451</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>731783</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7182808</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870451</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134870454</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>731779</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7182821</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870454</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134870456</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>731774</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7182830</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870456</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134870459</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>731739</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7182831</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870459</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134870461</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>731784</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7182829</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870461</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134870462</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>731791</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7182842</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870462</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134870465</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>731846</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7182858</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870465</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134870467</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>731832</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7182845</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870467</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134870473</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>731811</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7182810</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870473</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134870474</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>731807</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7182795</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870474</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134870475</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>731833</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7182786</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870475</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134870477</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>731833</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7182800</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870477</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134870481</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>731927</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7182797</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870481</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134870484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>731962</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7182738</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870484</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134870487</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>732024</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7182764</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870487</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134870488</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>732037</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7182780</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870488</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134870490</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>732066</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7182765</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870490</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134870494</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>732065</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7182745</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870494</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134870496</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>732062</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7182736</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bilder</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870496</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134870502</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>731967</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7182675</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870502</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134870491</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>732063</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7182760</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870491</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134870457</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>731740</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7182830</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870457</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134870460</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>731735</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7182822</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870460</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134870464</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>731836</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7182866</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870464</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134870466</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>731846</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7182858</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870466</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134870468</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>731828</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7182843</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870468</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134870469</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>731814</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7182829</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre barksprätt</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134870470</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>731821</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7182817</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2st skalade granar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870470</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134870476</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>731833</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7182791</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Barksprätt Färska</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870476</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134870479</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>731920</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7182781</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Skalade granar äldre</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870479</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134870480</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>731924</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7182785</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Skalad gran äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870480</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134870485</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>731969</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7182731</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Barksprätt färska</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870485</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134870486</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>732008</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7182769</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Skalad gran färsk</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870486</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134870493</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>732063</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7182758</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>äldre ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870493</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134870495</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>732067</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7182741</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska barksprätt</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870495</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134870497</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>732047</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7182705</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack bilder</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870497</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134870498</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>732038</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7182705</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack bilder</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870498</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134870501</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>731989</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7182674</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870501</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134870483</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>731953</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7182747</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I en gammtall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870483</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134870489</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58683</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>732071</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7182758</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>En mindre grupp</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870489</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134870472</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92440</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Rengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>731815</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7182829</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134870472</t>
         </is>
       </c>
     </row>
@@ -1195,6 +7751,60 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92408</v>
+        <v>92421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58683</v>
+        <v>58685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92421</v>
+        <v>92422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92422</v>
+        <v>92423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92423</v>
+        <v>92424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58685</v>
+        <v>58686</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92424</v>
+        <v>92430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58686</v>
+        <v>58690</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92430</v>
+        <v>92431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58690</v>
+        <v>58691</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92431</v>
+        <v>92437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92416</v>
+        <v>92422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92466</v>
+        <v>92472</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92437</v>
+        <v>92444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92422</v>
+        <v>92429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134870445</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>134870446</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134870451</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>134870454</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>134870456</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>134870459</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>134870461</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>134870462</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>134870465</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134870467</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>134870473</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134870474</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>134870475</v>
       </c>
       <c r="B30" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134870477</v>
       </c>
       <c r="B31" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>134870481</v>
       </c>
       <c r="B32" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>134870484</v>
       </c>
       <c r="B33" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>134870487</v>
       </c>
       <c r="B34" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>134870488</v>
       </c>
       <c r="B35" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>134870490</v>
       </c>
       <c r="B36" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134870494</v>
       </c>
       <c r="B37" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>134870496</v>
       </c>
       <c r="B38" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>134870502</v>
       </c>
       <c r="B39" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134870491</v>
       </c>
       <c r="B40" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>134870457</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>134870460</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>134870464</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>134870466</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>134870468</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>134870469</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>134870470</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>134870476</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>134870479</v>
       </c>
       <c r="B49" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>134870480</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>134870485</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>134870486</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>134870493</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>134870495</v>
       </c>
       <c r="B54" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134870497</v>
       </c>
       <c r="B55" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>134870498</v>
       </c>
       <c r="B56" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>134870501</v>
       </c>
       <c r="B57" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>134870483</v>
       </c>
       <c r="B58" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>134870489</v>
       </c>
       <c r="B59" t="n">
-        <v>58691</v>
+        <v>58696</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92472</v>
+        <v>92479</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27448-2026 artfynd.xlsx
+++ b/artfynd/A 27448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134870463</v>
       </c>
       <c r="B2" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134870447</v>
       </c>
       <c r="B3" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134870448</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>134870452</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>134870453</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134870455</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134870471</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>134870500</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>134870444</v>
       </c>
       <c r="B13" t="n">
-        <v>92444</v>
+        <v>92445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>134870449</v>
       </c>
       <c r="B14" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>134870482</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>134870472</v>
       </c>
       <c r="B60" t="n">
-        <v>92479</v>
+        <v>92480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
